--- a/SPM622 Group Project Documentation/Capstone_Project-for-SE2/06_Testing_Results_and_Evaluation/Customer_Support_Test_Cases_and_Results.xlsx
+++ b/SPM622 Group Project Documentation/Capstone_Project-for-SE2/06_Testing_Results_and_Evaluation/Customer_Support_Test_Cases_and_Results.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="146">
   <si>
     <t xml:space="preserve">Test ID</t>
   </si>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Dashboard loaded correctly</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_01.png</t>
+    <t xml:space="preserve">TC01_Admin_Dashboard.png</t>
   </si>
   <si>
     <t xml:space="preserve">Freek</t>
@@ -93,10 +93,10 @@
     <t xml:space="preserve">Ticket saved and visible</t>
   </si>
   <si>
-    <t xml:space="preserve">Ticket created and visible in list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screenshot_02.png</t>
+    <t xml:space="preserve">Ticket form loaded correctly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC02_New_Ticket_Form.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-03</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Ticket details loaded correctly</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_03.png</t>
+    <t xml:space="preserve">TC03_Ticket_Detail_View.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-04</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Agent assigned successfully</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_04.png</t>
+    <t xml:space="preserve">TC04_Ticket_Updated_Assigned.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-05</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Status updated to In Progress</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_05.png</t>
+    <t xml:space="preserve">TC05_Status_In_Progress.png</t>
   </si>
   <si>
     <t xml:space="preserve">Wian</t>
@@ -171,7 +171,7 @@
     <t xml:space="preserve">Comment displayed in timeline</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_06.png</t>
+    <t xml:space="preserve">TC06_Comment_Posted.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-07</t>
@@ -189,7 +189,7 @@
     <t xml:space="preserve">Status updated to Resolved</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_07.png</t>
+    <t xml:space="preserve">TC07_Status_Resolved.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-08</t>
@@ -207,7 +207,7 @@
     <t xml:space="preserve">Error shown correctly</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_08.png</t>
+    <t xml:space="preserve">TC08_Login_Error.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-09</t>
@@ -222,10 +222,10 @@
     <t xml:space="preserve">HTTP 403 Forbidden</t>
   </si>
   <si>
-    <t xml:space="preserve">403 page displayed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screenshot_09.png</t>
+    <t xml:space="preserve">Blocked by server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC09_403_Forbidden.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-10</t>
@@ -237,10 +237,7 @@
     <t xml:space="preserve">Customer tries to POST to update ticket</t>
   </si>
   <si>
-    <t xml:space="preserve">Blocked by server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screenshot_10.png</t>
+    <t xml:space="preserve">TC10_Role_Restriction.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-11</t>
@@ -258,7 +255,7 @@
     <t xml:space="preserve">Inline error shown</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_11.png</t>
+    <t xml:space="preserve">TC11_Validation_Empty_Title.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-12</t>
@@ -276,7 +273,7 @@
     <t xml:space="preserve">Blocked by validation</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_12.png</t>
+    <t xml:space="preserve">TC12_Priority_Dropdown.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-13</t>
@@ -291,7 +288,7 @@
     <t xml:space="preserve">Blocked by CSRF check</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_13.png</t>
+    <t xml:space="preserve">TC13_CSRF_Error_400.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-14</t>
@@ -309,7 +306,7 @@
     <t xml:space="preserve">Update successful</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_14.png</t>
+    <t xml:space="preserve">TC14_Assignee_Saved.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-15</t>
@@ -324,7 +321,7 @@
     <t xml:space="preserve">Status persists</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_15.png</t>
+    <t xml:space="preserve">TC15_Status_Update_Success.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-16</t>
@@ -342,7 +339,7 @@
     <t xml:space="preserve">Displayed correctly</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_16.png</t>
+    <t xml:space="preserve">TC16_Agent_Comment_Posted.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-17</t>
@@ -354,7 +351,7 @@
     <t xml:space="preserve">Status displayed as Resolved</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_17.png</t>
+    <t xml:space="preserve">TC17_Resolve_Ticket_Success.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-18</t>
@@ -372,7 +369,7 @@
     <t xml:space="preserve">Redirected securely</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_18.png</t>
+    <t xml:space="preserve">TC18_Logout_Redirect.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-19</t>
@@ -390,7 +387,7 @@
     <t xml:space="preserve">Counts verified</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_19.png</t>
+    <t xml:space="preserve">TC19_Dashboard_Stats.png</t>
   </si>
   <si>
     <t xml:space="preserve">TC-20</t>
@@ -408,7 +405,7 @@
     <t xml:space="preserve">Login failed safely</t>
   </si>
   <si>
-    <t xml:space="preserve">Screenshot_20.png</t>
+    <t xml:space="preserve">TC20_SQL_Injection_Blocked.png</t>
   </si>
   <si>
     <t xml:space="preserve">Test area</t>
@@ -563,8 +560,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -576,11 +577,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -880,623 +881,623 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="E5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="E6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="E8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="E9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="E10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="E11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I12" s="2" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="2" t="s">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" s="2" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H20" s="2" t="s">
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="I21" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1531,145 +1532,145 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="3" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="D8" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F8"/>
